--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129150506</v>
+        <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517057</v>
+        <v>517079</v>
       </c>
       <c r="R2" t="n">
-        <v>6718370</v>
+        <v>6718455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150506</t>
+          <t>https://artportalen.se/Sighting/136965652</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129150462</v>
+        <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>93233</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517071</v>
+        <v>517079</v>
       </c>
       <c r="R3" t="n">
-        <v>6718349</v>
+        <v>6718455</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150462</t>
+          <t>https://artportalen.se/Sighting/136965664</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128337675</v>
+        <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>8455</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516947</v>
+        <v>517079</v>
       </c>
       <c r="R4" t="n">
-        <v>6718566</v>
+        <v>6718455</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,21 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,63 +1010,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128337675</t>
+          <t>https://artportalen.se/Sighting/136965658</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128331155</v>
+        <v>129150506</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517237</v>
+        <v>517057</v>
       </c>
       <c r="R5" t="n">
-        <v>6718324</v>
+        <v>6718370</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,78 +1111,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128331155</t>
+          <t>https://artportalen.se/Sighting/129150506</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129011026</v>
+        <v>129150462</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517079</v>
+        <v>517071</v>
       </c>
       <c r="R6" t="n">
-        <v>6718455</v>
+        <v>6718349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,86 +1217,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011026</t>
+          <t>https://artportalen.se/Sighting/129150462</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129150241</v>
+        <v>128337675</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517130</v>
+        <v>516947</v>
       </c>
       <c r="R7" t="n">
-        <v>6718211</v>
+        <v>6718566</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,27 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,28 +1331,43 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150241</t>
+          <t>https://artportalen.se/Sighting/128337675</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129150280</v>
+        <v>128331155</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1442,17 +1397,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1461,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517115</v>
+        <v>517237</v>
       </c>
       <c r="R8" t="n">
-        <v>6718208</v>
+        <v>6718324</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,22 +1441,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,24 +1471,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150280</t>
+          <t>https://artportalen.se/Sighting/128331155</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129150830</v>
+        <v>129011026</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1568,32 +1518,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516973</v>
+        <v>517079</v>
       </c>
       <c r="R9" t="n">
-        <v>6718487</v>
+        <v>6718455</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,27 +1569,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter. Ej räknade.</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,22 +1593,411 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129150241</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517130</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6718211</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150241</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129150280</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6718208</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150280</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129150830</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516973</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6718487</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter. Ej räknade.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129150830</t>
         </is>
@@ -1677,6 +2013,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965652</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136965664</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136965658</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136965652</v>
+        <v>129150506</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517079</v>
+        <v>517057</v>
       </c>
       <c r="R2" t="n">
-        <v>6718455</v>
+        <v>6718370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136965652</t>
+          <t>https://artportalen.se/Sighting/129150506</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136965664</v>
+        <v>129150462</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517079</v>
+        <v>517071</v>
       </c>
       <c r="R3" t="n">
-        <v>6718455</v>
+        <v>6718349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136965664</t>
+          <t>https://artportalen.se/Sighting/129150462</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136965658</v>
+        <v>128337675</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gubbmyran, Dlr</t>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517079</v>
+        <v>516947</v>
       </c>
       <c r="R4" t="n">
-        <v>6718455</v>
+        <v>6718566</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,6 +995,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1010,54 +1025,63 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136965658</t>
+          <t>https://artportalen.se/Sighting/128337675</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129150506</v>
+        <v>128331155</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517057</v>
+        <v>517237</v>
       </c>
       <c r="R5" t="n">
-        <v>6718370</v>
+        <v>6718324</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1135,78 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150506</t>
+          <t>https://artportalen.se/Sighting/128331155</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129150462</v>
+        <v>129011026</v>
       </c>
       <c r="B6" t="n">
-        <v>93233</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517071</v>
+        <v>517079</v>
       </c>
       <c r="R6" t="n">
-        <v>6718349</v>
+        <v>6718455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,71 +1257,86 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150462</t>
+          <t>https://artportalen.se/Sighting/129011026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128337675</v>
+        <v>129150241</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516947</v>
+        <v>517130</v>
       </c>
       <c r="R7" t="n">
-        <v>6718566</v>
+        <v>6718211</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1360,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,43 +1391,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128337675</t>
+          <t>https://artportalen.se/Sighting/129150241</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128331155</v>
+        <v>129150280</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1397,12 +1442,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517237</v>
+        <v>517115</v>
       </c>
       <c r="R8" t="n">
-        <v>6718324</v>
+        <v>6718208</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1491,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,24 +1521,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128331155</t>
+          <t>https://artportalen.se/Sighting/129150280</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011026</v>
+        <v>129150830</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1518,34 +1568,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517079</v>
+        <v>516973</v>
       </c>
       <c r="R9" t="n">
-        <v>6718455</v>
+        <v>6718487</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,22 +1617,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter. Ej räknade.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,411 +1646,22 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129011026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>129150241</v>
-      </c>
-      <c r="B10" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>517130</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6718211</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129150241</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>129150280</v>
-      </c>
-      <c r="B11" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>517115</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6718208</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129150280</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>129150830</v>
-      </c>
-      <c r="B12" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Gubbmyran, Gubbmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>516973</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6718487</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter. Ej räknade.</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129150830</t>
         </is>
@@ -2013,9 +1677,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
